--- a/bkp/Cube_finish.xlsx
+++ b/bkp/Cube_finish.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Warley Souza\Music\read_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Warley Souza\Music\read_excel\bkp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCBC5AE-AE51-4312-B156-9687C193927D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0C8C9F-C1C0-41EE-94A9-E6C3DA59265A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="965">
   <si>
     <t>Cube</t>
   </si>
@@ -2892,6 +2892,30 @@
   </si>
   <si>
     <t>122D</t>
+  </si>
+  <si>
+    <t>3rd Floor Slab (19-33)(U-JJ)</t>
+  </si>
+  <si>
+    <t>3rd Floor Wall (U)(13-14), w1(U-Z)(16-19),W1(U-GG)(18),W1(DD-GG)(15-16),W1(12-17)(Z-GG)</t>
+  </si>
+  <si>
+    <t>3rd Floor Walls (19)(U-GG),W1 (18)(Z-DD),W1(16)(Z-DD),W1(13)(U-GG), W1(11)(DD-EE), W1( 5-7)(EE), W1(24-29)(Z-GG)</t>
+  </si>
+  <si>
+    <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+  </si>
+  <si>
+    <t>3rd Floor Slab (28-35)(U-Z),W1(27-34)(GG-JJ), W1(30)(U-GG)</t>
+  </si>
+  <si>
+    <t>3rd Floor Walls (19-20)(U), W1(22-25)(U-Z), W1(25-27)(P-Z), W1(27-28)(DD-GG), W1(23)(Z-GG), W1 (19-22)(Z-JJ)</t>
+  </si>
+  <si>
+    <t>117B</t>
+  </si>
+  <si>
+    <t>3rd Floor Walls (44-45)(K-GG), W1 (34-45)(EE-GG), W1(28)(U-DD)</t>
   </si>
 </sst>
 </file>
@@ -2953,7 +2977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2965,6 +2989,15 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17625,11 +17658,15 @@
       <c r="J581" s="2"/>
     </row>
     <row r="582" spans="1:10">
-      <c r="A582" s="2" t="s">
+      <c r="A582" s="7" t="s">
         <v>910</v>
       </c>
-      <c r="B582" s="5"/>
-      <c r="C582" s="2"/>
+      <c r="B582" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C582" s="8" t="s">
+        <v>957</v>
+      </c>
       <c r="D582" s="5"/>
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
@@ -17639,11 +17676,15 @@
       <c r="J582" s="2"/>
     </row>
     <row r="583" spans="1:10">
-      <c r="A583" s="2" t="s">
+      <c r="A583" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="B583" s="5"/>
-      <c r="C583" s="2"/>
+      <c r="B583" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C583" s="8" t="s">
+        <v>957</v>
+      </c>
       <c r="D583" s="5"/>
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
@@ -17653,11 +17694,15 @@
       <c r="J583" s="2"/>
     </row>
     <row r="584" spans="1:10">
-      <c r="A584" s="2" t="s">
+      <c r="A584" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="B584" s="5"/>
-      <c r="C584" s="2"/>
+      <c r="B584" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C584" s="8" t="s">
+        <v>957</v>
+      </c>
       <c r="D584" s="5"/>
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
@@ -17667,11 +17712,15 @@
       <c r="J584" s="2"/>
     </row>
     <row r="585" spans="1:10">
-      <c r="A585" s="2" t="s">
+      <c r="A585" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="B585" s="5"/>
-      <c r="C585" s="2"/>
+      <c r="B585" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C585" s="8" t="s">
+        <v>957</v>
+      </c>
       <c r="D585" s="5"/>
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
@@ -17681,11 +17730,15 @@
       <c r="J585" s="2"/>
     </row>
     <row r="586" spans="1:10">
-      <c r="A586" s="2" t="s">
+      <c r="A586" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="B586" s="5"/>
-      <c r="C586" s="2"/>
+      <c r="B586" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C586" s="8" t="s">
+        <v>958</v>
+      </c>
       <c r="D586" s="5"/>
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
@@ -17695,11 +17748,15 @@
       <c r="J586" s="2"/>
     </row>
     <row r="587" spans="1:10">
-      <c r="A587" s="2" t="s">
+      <c r="A587" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="B587" s="5"/>
-      <c r="C587" s="2"/>
+      <c r="B587" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C587" s="8" t="s">
+        <v>958</v>
+      </c>
       <c r="D587" s="5"/>
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
@@ -17709,11 +17766,15 @@
       <c r="J587" s="2"/>
     </row>
     <row r="588" spans="1:10">
-      <c r="A588" s="2" t="s">
+      <c r="A588" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="B588" s="5"/>
-      <c r="C588" s="2"/>
+      <c r="B588" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C588" s="8" t="s">
+        <v>958</v>
+      </c>
       <c r="D588" s="5"/>
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
@@ -17723,11 +17784,15 @@
       <c r="J588" s="2"/>
     </row>
     <row r="589" spans="1:10">
-      <c r="A589" s="2" t="s">
+      <c r="A589" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="B589" s="5"/>
-      <c r="C589" s="2"/>
+      <c r="B589" s="9">
+        <v>44627</v>
+      </c>
+      <c r="C589" s="8" t="s">
+        <v>958</v>
+      </c>
       <c r="D589" s="5"/>
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
@@ -17736,12 +17801,16 @@
       <c r="I589" s="2"/>
       <c r="J589" s="2"/>
     </row>
-    <row r="590" spans="1:10">
-      <c r="A590" s="2" t="s">
+    <row r="590" spans="1:10" ht="28.8">
+      <c r="A590" s="7" t="s">
         <v>919</v>
       </c>
-      <c r="B590" s="5"/>
-      <c r="C590" s="2"/>
+      <c r="B590" s="9">
+        <v>44629</v>
+      </c>
+      <c r="C590" s="8" t="s">
+        <v>959</v>
+      </c>
       <c r="D590" s="5"/>
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
@@ -17750,12 +17819,16 @@
       <c r="I590" s="2"/>
       <c r="J590" s="2"/>
     </row>
-    <row r="591" spans="1:10">
-      <c r="A591" s="2" t="s">
+    <row r="591" spans="1:10" ht="28.8">
+      <c r="A591" s="7" t="s">
         <v>920</v>
       </c>
-      <c r="B591" s="5"/>
-      <c r="C591" s="2"/>
+      <c r="B591" s="9">
+        <v>44629</v>
+      </c>
+      <c r="C591" s="8" t="s">
+        <v>959</v>
+      </c>
       <c r="D591" s="5"/>
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
@@ -17764,12 +17837,16 @@
       <c r="I591" s="2"/>
       <c r="J591" s="2"/>
     </row>
-    <row r="592" spans="1:10">
-      <c r="A592" s="2" t="s">
+    <row r="592" spans="1:10" ht="28.8">
+      <c r="A592" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="B592" s="5"/>
-      <c r="C592" s="2"/>
+      <c r="B592" s="9">
+        <v>44629</v>
+      </c>
+      <c r="C592" s="8" t="s">
+        <v>959</v>
+      </c>
       <c r="D592" s="5"/>
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
@@ -17778,12 +17855,16 @@
       <c r="I592" s="2"/>
       <c r="J592" s="2"/>
     </row>
-    <row r="593" spans="1:10">
-      <c r="A593" s="2" t="s">
+    <row r="593" spans="1:10" ht="28.8">
+      <c r="A593" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="B593" s="5"/>
-      <c r="C593" s="2"/>
+      <c r="B593" s="9">
+        <v>44629</v>
+      </c>
+      <c r="C593" s="8" t="s">
+        <v>959</v>
+      </c>
       <c r="D593" s="5"/>
       <c r="E593" s="2"/>
       <c r="F593" s="2"/>
@@ -17793,11 +17874,15 @@
       <c r="J593" s="2"/>
     </row>
     <row r="594" spans="1:10">
-      <c r="A594" s="2" t="s">
+      <c r="A594" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="B594" s="5"/>
-      <c r="C594" s="2"/>
+      <c r="B594" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C594" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D594" s="5"/>
       <c r="E594" s="2"/>
       <c r="F594" s="2"/>
@@ -17807,11 +17892,15 @@
       <c r="J594" s="2"/>
     </row>
     <row r="595" spans="1:10">
-      <c r="A595" s="2" t="s">
+      <c r="A595" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="B595" s="5"/>
-      <c r="C595" s="2"/>
+      <c r="B595" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C595" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D595" s="5"/>
       <c r="E595" s="2"/>
       <c r="F595" s="2"/>
@@ -17821,11 +17910,15 @@
       <c r="J595" s="2"/>
     </row>
     <row r="596" spans="1:10">
-      <c r="A596" s="2" t="s">
+      <c r="A596" s="7" t="s">
         <v>925</v>
       </c>
-      <c r="B596" s="5"/>
-      <c r="C596" s="2"/>
+      <c r="B596" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C596" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D596" s="5"/>
       <c r="E596" s="2"/>
       <c r="F596" s="2"/>
@@ -17835,11 +17928,15 @@
       <c r="J596" s="2"/>
     </row>
     <row r="597" spans="1:10">
-      <c r="A597" s="2" t="s">
+      <c r="A597" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="B597" s="5"/>
-      <c r="C597" s="2"/>
+      <c r="B597" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C597" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D597" s="5"/>
       <c r="E597" s="2"/>
       <c r="F597" s="2"/>
@@ -17849,11 +17946,15 @@
       <c r="J597" s="2"/>
     </row>
     <row r="598" spans="1:10">
-      <c r="A598" s="2" t="s">
+      <c r="A598" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="B598" s="5"/>
-      <c r="C598" s="2"/>
+      <c r="B598" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C598" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D598" s="5"/>
       <c r="E598" s="2"/>
       <c r="F598" s="2"/>
@@ -17863,11 +17964,15 @@
       <c r="J598" s="2"/>
     </row>
     <row r="599" spans="1:10">
-      <c r="A599" s="2" t="s">
+      <c r="A599" s="7" t="s">
         <v>928</v>
       </c>
-      <c r="B599" s="5"/>
-      <c r="C599" s="2"/>
+      <c r="B599" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C599" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D599" s="5"/>
       <c r="E599" s="2"/>
       <c r="F599" s="2"/>
@@ -17877,11 +17982,15 @@
       <c r="J599" s="2"/>
     </row>
     <row r="600" spans="1:10">
-      <c r="A600" s="2" t="s">
+      <c r="A600" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="B600" s="5"/>
-      <c r="C600" s="2"/>
+      <c r="B600" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C600" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D600" s="5"/>
       <c r="E600" s="2"/>
       <c r="F600" s="2"/>
@@ -17891,11 +18000,15 @@
       <c r="J600" s="2"/>
     </row>
     <row r="601" spans="1:10">
-      <c r="A601" s="2" t="s">
+      <c r="A601" s="7" t="s">
         <v>930</v>
       </c>
-      <c r="B601" s="5"/>
-      <c r="C601" s="2"/>
+      <c r="B601" s="9">
+        <v>44630</v>
+      </c>
+      <c r="C601" s="8" t="s">
+        <v>960</v>
+      </c>
       <c r="D601" s="5"/>
       <c r="E601" s="2"/>
       <c r="F601" s="2"/>
@@ -17905,11 +18018,15 @@
       <c r="J601" s="2"/>
     </row>
     <row r="602" spans="1:10">
-      <c r="A602" s="2" t="s">
+      <c r="A602" s="7" t="s">
         <v>931</v>
       </c>
-      <c r="B602" s="5"/>
-      <c r="C602" s="2"/>
+      <c r="B602" s="9">
+        <v>44631</v>
+      </c>
+      <c r="C602" s="8" t="s">
+        <v>961</v>
+      </c>
       <c r="D602" s="5"/>
       <c r="E602" s="2"/>
       <c r="F602" s="2"/>
@@ -17919,11 +18036,15 @@
       <c r="J602" s="2"/>
     </row>
     <row r="603" spans="1:10">
-      <c r="A603" s="2" t="s">
+      <c r="A603" s="7" t="s">
         <v>932</v>
       </c>
-      <c r="B603" s="5"/>
-      <c r="C603" s="2"/>
+      <c r="B603" s="9">
+        <v>44631</v>
+      </c>
+      <c r="C603" s="8" t="s">
+        <v>961</v>
+      </c>
       <c r="D603" s="5"/>
       <c r="E603" s="2"/>
       <c r="F603" s="2"/>
@@ -17933,11 +18054,15 @@
       <c r="J603" s="2"/>
     </row>
     <row r="604" spans="1:10">
-      <c r="A604" s="2" t="s">
+      <c r="A604" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="B604" s="5"/>
-      <c r="C604" s="2"/>
+      <c r="B604" s="9">
+        <v>44631</v>
+      </c>
+      <c r="C604" s="8" t="s">
+        <v>961</v>
+      </c>
       <c r="D604" s="5"/>
       <c r="E604" s="2"/>
       <c r="F604" s="2"/>
@@ -17947,11 +18072,15 @@
       <c r="J604" s="2"/>
     </row>
     <row r="605" spans="1:10">
-      <c r="A605" s="2" t="s">
+      <c r="A605" s="7" t="s">
         <v>934</v>
       </c>
-      <c r="B605" s="5"/>
-      <c r="C605" s="2"/>
+      <c r="B605" s="9">
+        <v>44631</v>
+      </c>
+      <c r="C605" s="8" t="s">
+        <v>961</v>
+      </c>
       <c r="D605" s="5"/>
       <c r="E605" s="2"/>
       <c r="F605" s="2"/>
@@ -17960,12 +18089,16 @@
       <c r="I605" s="2"/>
       <c r="J605" s="2"/>
     </row>
-    <row r="606" spans="1:10">
-      <c r="A606" s="2" t="s">
+    <row r="606" spans="1:10" ht="28.8">
+      <c r="A606" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="B606" s="5"/>
-      <c r="C606" s="2"/>
+      <c r="B606" s="9">
+        <v>44634</v>
+      </c>
+      <c r="C606" s="8" t="s">
+        <v>962</v>
+      </c>
       <c r="D606" s="5"/>
       <c r="E606" s="2"/>
       <c r="F606" s="2"/>
@@ -17974,12 +18107,16 @@
       <c r="I606" s="2"/>
       <c r="J606" s="2"/>
     </row>
-    <row r="607" spans="1:10">
-      <c r="A607" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B607" s="5"/>
-      <c r="C607" s="2"/>
+    <row r="607" spans="1:10" ht="28.8">
+      <c r="A607" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="B607" s="9">
+        <v>44634</v>
+      </c>
+      <c r="C607" s="8" t="s">
+        <v>962</v>
+      </c>
       <c r="D607" s="5"/>
       <c r="E607" s="2"/>
       <c r="F607" s="2"/>
@@ -17988,12 +18125,16 @@
       <c r="I607" s="2"/>
       <c r="J607" s="2"/>
     </row>
-    <row r="608" spans="1:10">
-      <c r="A608" s="2" t="s">
+    <row r="608" spans="1:10" ht="28.8">
+      <c r="A608" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="B608" s="5"/>
-      <c r="C608" s="2"/>
+      <c r="B608" s="9">
+        <v>44634</v>
+      </c>
+      <c r="C608" s="8" t="s">
+        <v>962</v>
+      </c>
       <c r="D608" s="5"/>
       <c r="E608" s="2"/>
       <c r="F608" s="2"/>
@@ -18002,12 +18143,16 @@
       <c r="I608" s="2"/>
       <c r="J608" s="2"/>
     </row>
-    <row r="609" spans="1:10">
-      <c r="A609" s="2" t="s">
+    <row r="609" spans="1:10" ht="28.8">
+      <c r="A609" s="7" t="s">
         <v>937</v>
       </c>
-      <c r="B609" s="5"/>
-      <c r="C609" s="2"/>
+      <c r="B609" s="9">
+        <v>44634</v>
+      </c>
+      <c r="C609" s="8" t="s">
+        <v>962</v>
+      </c>
       <c r="D609" s="5"/>
       <c r="E609" s="2"/>
       <c r="F609" s="2"/>
@@ -18017,11 +18162,15 @@
       <c r="J609" s="2"/>
     </row>
     <row r="610" spans="1:10">
-      <c r="A610" s="2" t="s">
+      <c r="A610" s="7" t="s">
         <v>938</v>
       </c>
-      <c r="B610" s="5"/>
-      <c r="C610" s="2"/>
+      <c r="B610" s="9">
+        <v>44635</v>
+      </c>
+      <c r="C610" s="8" t="s">
+        <v>964</v>
+      </c>
       <c r="D610" s="5"/>
       <c r="E610" s="2"/>
       <c r="F610" s="2"/>
@@ -18031,11 +18180,15 @@
       <c r="J610" s="2"/>
     </row>
     <row r="611" spans="1:10">
-      <c r="A611" s="2" t="s">
+      <c r="A611" s="7" t="s">
         <v>939</v>
       </c>
-      <c r="B611" s="5"/>
-      <c r="C611" s="2"/>
+      <c r="B611" s="9">
+        <v>44635</v>
+      </c>
+      <c r="C611" s="8" t="s">
+        <v>964</v>
+      </c>
       <c r="D611" s="5"/>
       <c r="E611" s="2"/>
       <c r="F611" s="2"/>
@@ -18045,11 +18198,15 @@
       <c r="J611" s="2"/>
     </row>
     <row r="612" spans="1:10">
-      <c r="A612" s="2" t="s">
+      <c r="A612" s="7" t="s">
         <v>940</v>
       </c>
-      <c r="B612" s="5"/>
-      <c r="C612" s="2"/>
+      <c r="B612" s="9">
+        <v>44635</v>
+      </c>
+      <c r="C612" s="8" t="s">
+        <v>964</v>
+      </c>
       <c r="D612" s="5"/>
       <c r="E612" s="2"/>
       <c r="F612" s="2"/>
@@ -18059,11 +18216,15 @@
       <c r="J612" s="2"/>
     </row>
     <row r="613" spans="1:10">
-      <c r="A613" s="2" t="s">
+      <c r="A613" s="7" t="s">
         <v>941</v>
       </c>
-      <c r="B613" s="5"/>
-      <c r="C613" s="2"/>
+      <c r="B613" s="9">
+        <v>44635</v>
+      </c>
+      <c r="C613" s="8" t="s">
+        <v>964</v>
+      </c>
       <c r="D613" s="5"/>
       <c r="E613" s="2"/>
       <c r="F613" s="2"/>
